--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525415</v>
+        <v>121525418</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525450</v>
+        <v>121525415</v>
       </c>
       <c r="B3" t="n">
-        <v>94870</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R3" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,18 +899,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525405</v>
+        <v>121525450</v>
       </c>
       <c r="B4" t="n">
-        <v>90733</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585224</v>
+        <v>585243</v>
       </c>
       <c r="R4" t="n">
-        <v>6345019</v>
+        <v>6344965</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,6 +1013,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1048,7 @@
         <v>121525411</v>
       </c>
       <c r="B5" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1158,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525418</v>
+        <v>121525405</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>90739</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,39 +1174,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585209</v>
+        <v>585224</v>
       </c>
       <c r="R6" t="n">
-        <v>6345042</v>
+        <v>6345019</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,6 +1263,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525418</v>
+        <v>121525411</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>94877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525415</v>
+        <v>121525418</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +804,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,7 +827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -926,7 +919,7 @@
         <v>121525450</v>
       </c>
       <c r="B4" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1045,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525411</v>
+        <v>121525415</v>
       </c>
       <c r="B5" t="n">
-        <v>94876</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,31 +1050,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1143,7 +1144,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>121525405</v>
       </c>
       <c r="B6" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B2" t="n">
-        <v>94877</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525418</v>
+        <v>121525415</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -1038,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525415</v>
+        <v>121525411</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>94877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,39 +1057,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1144,6 +1143,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525418</v>
+        <v>121525411</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>94877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525415</v>
+        <v>121525450</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R3" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,12 +884,18 @@
           <t>10:30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525450</v>
+        <v>121525418</v>
       </c>
       <c r="B4" t="n">
-        <v>94877</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,27 +930,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R4" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,18 +1014,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1045,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525411</v>
+        <v>121525415</v>
       </c>
       <c r="B5" t="n">
-        <v>94877</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,31 +1050,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1143,7 +1144,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -785,17 +785,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525450</v>
+        <v>121525415</v>
       </c>
       <c r="B3" t="n">
-        <v>94877</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R3" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,18 +892,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,17 +909,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525418</v>
+        <v>121525405</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,39 +928,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585209</v>
+        <v>585224</v>
       </c>
       <c r="R4" t="n">
-        <v>6345042</v>
+        <v>6345019</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1020,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,17 +1029,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525415</v>
+        <v>121525450</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>94877</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,39 +1048,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R5" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,12 +1128,18 @@
           <t>10:30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1155,17 +1151,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525405</v>
+        <v>121525418</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>57725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,34 +1170,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1209,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585224</v>
+        <v>585209</v>
       </c>
       <c r="R6" t="n">
-        <v>6345019</v>
+        <v>6345042</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1263,7 +1264,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525405</v>
+        <v>121525415</v>
       </c>
       <c r="B2" t="n">
-        <v>90748</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,8 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585224</v>
+        <v>585209</v>
       </c>
       <c r="R2" t="n">
-        <v>6345019</v>
+        <v>6345042</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525450</v>
+        <v>121525405</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>90748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +811,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585243</v>
+        <v>585224</v>
       </c>
       <c r="R3" t="n">
-        <v>6344965</v>
+        <v>6345019</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,11 +892,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525415</v>
+        <v>121525411</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1023,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,27 +1052,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1139,7 +1142,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525418</v>
+        <v>121525450</v>
       </c>
       <c r="B6" t="n">
-        <v>57726</v>
+        <v>94885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,35 +1176,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R6" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,12 +1252,18 @@
           <t>10:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,27 +935,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1017,7 +1025,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525418</v>
+        <v>121525411</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>94885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1059,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1142,6 +1141,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525415</v>
+        <v>121525405</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>90748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585209</v>
+        <v>585224</v>
       </c>
       <c r="R2" t="n">
-        <v>6345042</v>
+        <v>6345019</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525405</v>
+        <v>121525415</v>
       </c>
       <c r="B3" t="n">
-        <v>90748</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,8 +833,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585224</v>
+        <v>585209</v>
       </c>
       <c r="R3" t="n">
-        <v>6345019</v>
+        <v>6345042</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +901,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525418</v>
+        <v>121525450</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,35 +935,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R4" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1019,12 +1011,18 @@
           <t>10:30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1043,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,27 +1057,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1141,7 +1147,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,7 +1165,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525450</v>
+        <v>121525411</v>
       </c>
       <c r="B6" t="n">
         <v>94885</v>
@@ -1204,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R6" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,11 +1255,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525405</v>
+        <v>121525411</v>
       </c>
       <c r="B2" t="n">
-        <v>90748</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585224</v>
+        <v>585209</v>
       </c>
       <c r="R2" t="n">
-        <v>6345019</v>
+        <v>6345042</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -1041,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525418</v>
+        <v>121525405</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,39 +1050,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585209</v>
+        <v>585224</v>
       </c>
       <c r="R5" t="n">
-        <v>6345042</v>
+        <v>6345019</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1147,6 +1139,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1165,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,27 +1174,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1263,7 +1264,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525411</v>
+        <v>121525418</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525415</v>
+        <v>121525411</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -898,6 +897,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525450</v>
+        <v>121525415</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,31 +928,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R4" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,18 +1016,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1158,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525418</v>
+        <v>121525450</v>
       </c>
       <c r="B6" t="n">
-        <v>57726</v>
+        <v>94885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,35 +1176,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1210,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R6" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,12 +1252,18 @@
           <t>10:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4645-2023 artfynd.xlsx
+++ b/artfynd/A 4645-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121525418</v>
+        <v>121525405</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>90748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585209</v>
+        <v>585224</v>
       </c>
       <c r="R2" t="n">
-        <v>6345042</v>
+        <v>6345019</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121525411</v>
+        <v>121525450</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585209</v>
+        <v>585243</v>
       </c>
       <c r="R3" t="n">
-        <v>6345042</v>
+        <v>6344965</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,6 +885,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stora bestånd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121525415</v>
+        <v>121525411</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,39 +929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1022,6 +1015,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121525405</v>
+        <v>121525415</v>
       </c>
       <c r="B5" t="n">
-        <v>90748</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,21 +1050,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1078,8 +1072,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585224</v>
+        <v>585209</v>
       </c>
       <c r="R5" t="n">
-        <v>6345019</v>
+        <v>6345042</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1140,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121525450</v>
+        <v>121525418</v>
       </c>
       <c r="B6" t="n">
-        <v>94885</v>
+        <v>57726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,27 +1174,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585243</v>
+        <v>585209</v>
       </c>
       <c r="R6" t="n">
-        <v>6344965</v>
+        <v>6345042</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,18 +1258,12 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stora bestånd</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
